--- a/mockups/Datos_necesarios_cuadro_Natalidad_v2.xlsx
+++ b/mockups/Datos_necesarios_cuadro_Natalidad_v2.xlsx
@@ -1834,8 +1834,8 @@
   <autoFilter ref="A4:E69"/>
   <mergeCells count="10">
     <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A11:E11"/>
